--- a/docs/configs/MetaData.xlsx
+++ b/docs/configs/MetaData.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,11 +29,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -45,8 +41,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
+        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -68,11 +63,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,372 +433,412 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>天赋ID</t>
+          <t>编号</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>描述</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>最大等级</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>基础费用</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>费用增长倍率</t>
-        </is>
-      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>费用增长</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>图标</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>string:client</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>string:client</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>string:client</t>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>Desc</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>MaxLv</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>CostBase</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>CostGrow</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>Icon</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>hp</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>生命强化</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>列车最大HP+10</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="E4" t="n">
         <v>10</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="F4" t="n">
         <v>50</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="G4" t="n">
         <v>1.3</v>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>image/talent_hp_20260421065056.png</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>atk</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>力量提升</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>攻击力+1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="E5" t="n">
         <v>10</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="F5" t="n">
         <v>60</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="G5" t="n">
         <v>1.3</v>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>image/talent_atk_20260421065251.png</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>atkspd</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>疾速打击</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>攻击速度+5%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="E6" t="n">
         <v>8</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="F6" t="n">
         <v>80</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="G6" t="n">
         <v>1.4</v>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>image/talent_atkspd_20260421065058.png</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>def</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>铁壁防御</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>减少列车受伤-5%</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="E7" t="n">
         <v>8</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="F7" t="n">
         <v>70</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="G7" t="n">
         <v>1.3</v>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>image/talent_def_20260421065053.png</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>speed</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>轻身术</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>移动速度+8%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="E8" t="n">
         <v>6</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="F8" t="n">
         <v>60</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="G8" t="n">
         <v>1.4</v>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>image/talent_speed_20260421065223.png</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>聚财术</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>金币收益+10%</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="E9" t="n">
         <v>8</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="F9" t="n">
         <v>100</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="G9" t="n">
         <v>1.5</v>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>image/talent_gold_20260421065059.png</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>carry</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>负重训练</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>携带上限+2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="E10" t="n">
         <v>5</v>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="F10" t="n">
         <v>80</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="G10" t="n">
         <v>1.4</v>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>image/talent_carry_20260421065057.png</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>unlock</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>求生本能</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>解锁新技能</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="E11" t="n">
         <v>3</v>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="F11" t="n">
         <v>200</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="G11" t="n">
         <v>2</v>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>image/talent_unlock_20260421065109.png</t>
         </is>
@@ -823,10 +858,10 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
@@ -834,7 +869,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>关卡ID</t>
+          <t>编号</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -849,225 +884,225 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>金币奖励</t>
+          <t>奖励金币</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>宝箱类型</t>
+          <t>宝箱品质</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>默认解锁</t>
+          <t>是否解锁</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>string:client</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>Waves</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>RewardGold</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Chest</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>Unlocked</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>荒原前哨</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" t="n">
         <v>5</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" t="n">
         <v>50</v>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>bronze</t>
         </is>
       </c>
-      <c r="F4" s="2" t="b">
+      <c r="F4" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>冰封隧道</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" t="n">
         <v>7</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" t="n">
         <v>80</v>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>bronze</t>
         </is>
       </c>
-      <c r="F5" s="2" t="b">
+      <c r="F5" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>暴风雪谷</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" t="n">
         <v>8</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" t="n">
         <v>100</v>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>silver</t>
         </is>
       </c>
-      <c r="F6" s="2" t="b">
+      <c r="F6" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>死寂车站</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" t="n">
         <v>10</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" t="n">
         <v>150</v>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>silver</t>
         </is>
       </c>
-      <c r="F7" s="2" t="b">
+      <c r="F7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>钢铁废墟</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C8" t="n">
         <v>12</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" t="n">
         <v>200</v>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="F8" s="2" t="b">
+      <c r="F8" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>末日核心</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C9" t="n">
         <v>15</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" t="n">
         <v>300</v>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="F9" s="2" t="b">
+      <c r="F9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1082,264 +1117,298 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>炮塔ID</t>
+          <t>编号</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>最大等级</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>基础碎片</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>碎片增长倍率</t>
+          <t>碎片基数</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>碎片增长</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>图标</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>string:client</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>string:client</t>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>MaxLv</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>FragBase</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>FragGrow</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>Icon</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>arrow</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>弓箭炮塔</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="E4" t="n">
         <v>5</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="F4" t="n">
         <v>1.5</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>image/turret_arrow_v3_20260420035036.png</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>minigun</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>机关枪塔</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="E5" t="n">
         <v>8</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="F5" t="n">
         <v>1.5</v>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>image/turret_minigun_v3_20260420035022.png</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>flame</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>喷火炮塔</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="E6" t="n">
         <v>8</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="F6" t="n">
         <v>1.5</v>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>image/edited_turret_flame_nofire_20260423065123.png</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>sniper</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>狙击炮塔</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="E7" t="n">
         <v>10</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="F7" t="n">
         <v>1.6</v>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>image/turret_sniper_v3_20260420035021.png</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>electric</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>电能炮塔</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="E8" t="n">
         <v>10</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="F8" t="n">
         <v>1.6</v>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>image/turret_electric_v10_20260423040517.png</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>rocket</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>火箭炮塔</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="D9" t="n">
         <v>5</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="E9" t="n">
         <v>12</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="F9" t="n">
         <v>1.8</v>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>image/turret_rocket_v3_20260420035019.png</t>
         </is>
